--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:20</t>
+    <t xml:space="preserve">2026-09-29 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:11</t>
+    <t xml:space="preserve">2026-09-29 18:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>86.44</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>66.08</v>
+        <v>66.09</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>19.81</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>93.27</v>
+        <v>93.26</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>73.46</v>
@@ -547,7 +547,7 @@
         <v>6.56</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>62.01</v>
+        <v>62.02</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>55.45</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:47</t>
+    <t xml:space="preserve">2026-10-05 04:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>20.36</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>86.44</v>
+        <v>86.45</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>66.09</v>
@@ -519,7 +519,7 @@
         <v>19.81</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>93.26</v>
+        <v>93.27</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>73.46</v>
@@ -550,7 +550,7 @@
         <v>62.02</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>55.45</v>
+        <v>55.46</v>
       </c>
     </row>
     <row r="6">
@@ -589,10 +589,10 @@
         <v>-0.83</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>55.12</v>
+        <v>55.13</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>55.95</v>
+        <v>55.96</v>
       </c>
     </row>
     <row r="9">
